--- a/kanban_system/output/library_linked/UNECE法规清单.xlsx
+++ b/kanban_system/output/library_linked/UNECE法规清单.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3260" yWindow="3110" windowWidth="14400" windowHeight="8170" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ECE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="草案" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WP.29 提案追踪 · 母看板" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="单法规追踪·子看板" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ECE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="草案" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="WP.29 提案追踪 · 母看板" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="单法规追踪·子看板" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="更新" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ECE'!$A$1:$Y$154</definedName>
@@ -12236,6 +12236,11 @@
         </is>
       </c>
       <c r="Y99" s="26" t="n"/>
+      <c r="Z99" s="154" t="inlineStr">
+        <is>
+          <t>INS-2026-015 驾驶员前方视野校核指南 | GB 11562-2025</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="n">
@@ -16916,7 +16921,7 @@
       <c r="Y147" s="26" t="n"/>
       <c r="Z147" s="154" t="inlineStr">
         <is>
-          <t>INS-2026-008 国内首个车载HUD法规正式发布：区域1和区域2要求详解</t>
+          <t>INS-2026-008 国内首个车载HUD法规正式发布：区域1和区域2要求详解 ; INS-2026-015 驾驶员前方视野校核指南 | GB 11562-2025</t>
         </is>
       </c>
     </row>

--- a/kanban_system/output/library_linked/UNECE法规清单.xlsx
+++ b/kanban_system/output/library_linked/UNECE法规清单.xlsx
@@ -7984,6 +7984,11 @@
         </is>
       </c>
       <c r="Y55" s="26" t="n"/>
+      <c r="Z55" s="154" t="inlineStr">
+        <is>
+          <t>INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="n">
@@ -9634,6 +9639,11 @@
         </is>
       </c>
       <c r="Y72" s="26" t="n"/>
+      <c r="Z72" s="154" t="inlineStr">
+        <is>
+          <t>INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="n">
@@ -9733,7 +9743,7 @@
       <c r="Y73" s="26" t="n"/>
       <c r="Z73" s="154" t="inlineStr">
         <is>
-          <t>INS-2026-019 巴西认证为何混合联合国、美国法规？ECE、UN R、CONTRAN与RESOLUTION的区别</t>
+          <t>INS-2026-019 巴西认证为何混合联合国、美国法规？ECE、UN R、CONTRAN与RESOLUTION的区别 ; INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
         </is>
       </c>
     </row>
